--- a/TASK2/Scenariji/SC11_KonfiguracijaCijenaClanarina.xlsx
+++ b/TASK2/Scenariji/SC11_KonfiguracijaCijenaClanarina.xlsx
@@ -461,7 +461,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>Konfiguracija cijena clanarina</t>
+          <t>Konfiguracija cijena članarina</t>
         </is>
       </c>
     </row>
@@ -473,7 +473,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Administrator konfigurira cijene razlicitih tipova clanarina.</t>
+          <t>Administrator konfigurira cijene različitih tipova članarina.</t>
         </is>
       </c>
     </row>
@@ -485,7 +485,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Podrska za tri tipa clanarina (mjesecna, kvartalna, godisnja)</t>
+          <t>Podrska za tri tipa članarina (mjesecna, kvartalna, godisnja)</t>
         </is>
       </c>
     </row>
@@ -504,24 +504,24 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Posljedice - uspjesan zavrsetak</t>
+          <t>Posljedice - uspješan završetak</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Cijena clanarine je azurirana, nove kupovine koriste novu cijenu.</t>
+          <t>Cijena članarine je ažurirana, nove kupovine koriste novu cijenu.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Posljedice - neuspjesan zavrsetak</t>
+          <t>Posljedice - neuspješan završetak</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Cijena nije azurirana zbog nevalidne vrijednosti.</t>
+          <t>Cijena nije ažurirana zbog nevalidne vrijednosti.</t>
         </is>
       </c>
     </row>
@@ -557,7 +557,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Administrator pregledava cijene, mijenja odabranu cijenu, sistem azurira.</t>
+          <t>Administrator pregledava cijene, mijenja odabranu cijenu, sistem ažurira.</t>
         </is>
       </c>
     </row>
@@ -573,6 +573,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
@@ -602,14 +603,14 @@
     <row r="15">
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>2. Prikaz trenutnih cijena svih tipova clanarina</t>
+          <t>2. Prikaz trenutnih cijena svih tipova članarina</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>3. Odabir tipa clanarine za izmjenu</t>
+          <t>3. Odabir tipa članarine za izmjenu</t>
         </is>
       </c>
     </row>
@@ -637,7 +638,7 @@
     <row r="20">
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>7. Azuriranje cijene u sistemu</t>
+          <t>7. Ažuriranje cijene u sistemu</t>
         </is>
       </c>
     </row>
@@ -648,6 +649,7 @@
         </is>
       </c>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
